--- a/Bike-Repair-Source-Workbooks/Bike-Repair-Module-3-1.xlsx
+++ b/Bike-Repair-Source-Workbooks/Bike-Repair-Module-3-1.xlsx
@@ -74,7 +74,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -102,11 +102,12 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -138,6 +139,8 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1940,7 +1943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="B1:D63"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2011,7 +2014,7 @@
           <t>Fixtures — Company received at formation (June 1)</t>
         </is>
       </c>
-      <c r="C7" s="17" t="n"/>
+      <c r="C7" s="22" t="n"/>
       <c r="D7" s="4" t="n">
         <v>750</v>
       </c>
@@ -2022,7 +2025,7 @@
           <t>Laptop — Company received at formation (June 1)</t>
         </is>
       </c>
-      <c r="C8" s="17" t="n"/>
+      <c r="C8" s="22" t="n"/>
       <c r="D8" s="4" t="n">
         <v>610</v>
       </c>
@@ -2144,7 +2147,7 @@
           <t>Parts used — Priya S.</t>
         </is>
       </c>
-      <c r="C20" s="17" t="n"/>
+      <c r="C20" s="22" t="n"/>
       <c r="D20" s="4" t="n">
         <v>-25</v>
       </c>

--- a/Bike-Repair-Source-Workbooks/Bike-Repair-Module-3-1.xlsx
+++ b/Bike-Repair-Source-Workbooks/Bike-Repair-Module-3-1.xlsx
@@ -2008,7 +2008,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="7" collapsed="1">
+    <row r="7" hidden="1" outlineLevel="1">
       <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Fixtures — Company received at formation (June 1)</t>
@@ -2019,7 +2019,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="1" outlineLevel="1">
       <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Laptop — Company received at formation (June 1)</t>
@@ -2030,7 +2030,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="1" outlineLevel="1">
       <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Credit Card — Company assumed the claim at formation (June 1)</t>
@@ -2040,7 +2040,7 @@
         <v>-2030</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="1" outlineLevel="1">
       <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Customer Deposit — Company assumed the claim at formation (June 1)</t>
@@ -2051,7 +2051,7 @@
         <v>-220</v>
       </c>
     </row>
-    <row r="11" hidden="1" outlineLevel="1">
+    <row r="11" collapsed="1">
       <c r="B11" s="16" t="inlineStr">
         <is>
           <t>Balance, June 1, 2026</t>
@@ -2064,7 +2064,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" hidden="1" outlineLevel="1">
+    <row r="12">
       <c r="B12" s="16" t="inlineStr">
         <is>
           <t>Balance, August 31, 2026</t>
@@ -2077,11 +2077,11 @@
         <v/>
       </c>
     </row>
-    <row r="13" hidden="1" outlineLevel="1">
+    <row r="13">
       <c r="B13" s="3" t="n"/>
       <c r="D13" s="4" t="n"/>
     </row>
-    <row r="14" hidden="1" outlineLevel="1">
+    <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
           <t>GENERATED</t>
@@ -2090,7 +2090,7 @@
       <c r="C14" s="11" t="n"/>
       <c r="D14" s="11" t="n"/>
     </row>
-    <row r="15" hidden="1" outlineLevel="1">
+    <row r="15">
       <c r="B15" s="16" t="inlineStr">
         <is>
           <t>Balance, June 1, 2026</t>
@@ -2141,7 +2141,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="20" collapsed="1">
+    <row r="20" hidden="1" outlineLevel="1">
       <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Parts used — Priya S.</t>
@@ -2522,7 +2522,7 @@
         <v>-36</v>
       </c>
     </row>
-    <row r="58" hidden="1" outlineLevel="1">
+    <row r="58" collapsed="1">
       <c r="B58" s="16" t="inlineStr">
         <is>
           <t>Balance, August 31, 2026</t>
@@ -2535,11 +2535,11 @@
         <v/>
       </c>
     </row>
-    <row r="59" hidden="1" outlineLevel="1">
+    <row r="59">
       <c r="B59" s="3" t="n"/>
       <c r="D59" s="4" t="n"/>
     </row>
-    <row r="60" hidden="1" outlineLevel="1">
+    <row r="60">
       <c r="B60" s="6" t="inlineStr">
         <is>
           <t>WITHDRAWN</t>
@@ -2548,7 +2548,7 @@
       <c r="C60" s="11" t="n"/>
       <c r="D60" s="11" t="n"/>
     </row>
-    <row r="61" hidden="1" outlineLevel="1">
+    <row r="61">
       <c r="B61" s="16" t="inlineStr">
         <is>
           <t>Balance, June 1, 2026</t>

--- a/Bike-Repair-Source-Workbooks/Bike-Repair-Module-3-1.xlsx
+++ b/Bike-Repair-Source-Workbooks/Bike-Repair-Module-3-1.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D126"/>
+  <dimension ref="B1:D94"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -535,170 +535,171 @@
     <row r="3" hidden="1" outlineLevel="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Rent paid in advance (the lease)</t>
+          <t>Company received at formation (June 1)</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-1300</v>
-      </c>
-    </row>
-    <row r="4" hidden="1" outlineLevel="1">
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Park Tool repair stand</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>-200</v>
-      </c>
-    </row>
-    <row r="5" hidden="1" outlineLevel="1">
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Repair, customer paid</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="6" hidden="1" outlineLevel="1">
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Repair, customer paid</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="7" hidden="1" outlineLevel="1">
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Repair, customer paid</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" hidden="1" outlineLevel="1">
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Repair, customer paid</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="9" hidden="1" outlineLevel="1">
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Repair, customer paid</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="10" hidden="1" outlineLevel="1">
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Smith's deposit received</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="11" hidden="1" outlineLevel="1">
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Repair, customer paid</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" hidden="1" outlineLevel="1">
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Repair, customer paid</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="13" hidden="1" outlineLevel="1">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Covered from your personal funds</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="14" hidden="1" outlineLevel="1">
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Deposited to open the LLC bank account</t>
-        </is>
-      </c>
-      <c r="D14" s="15" t="n">
         <v>1300</v>
       </c>
     </row>
-    <row r="15" collapsed="1">
-      <c r="B15" s="16" t="inlineStr">
+    <row r="4" collapsed="1">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Balance, June 1, 2026</t>
         </is>
       </c>
-      <c r="C15" s="17" t="n"/>
-      <c r="D15" s="13">
-        <f>SUBTOTAL(9,D3:D14)</f>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="13">
+        <f>SUM(D3:D3)</f>
         <v>1300</v>
         <v/>
       </c>
     </row>
+    <row r="5" hidden="1" outlineLevel="1">
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Repair collected — Dana R.</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" hidden="1" outlineLevel="1">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Repair collected — Marcus T.</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" hidden="1" outlineLevel="1">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Repair collected — Priya S.</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="8" hidden="1" outlineLevel="1">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Repair collected — Liam O.</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="9" hidden="1" outlineLevel="1">
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Repair collected — Sofia M.</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" hidden="1" outlineLevel="1">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Repair collected — Jamal W.</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="11" hidden="1" outlineLevel="1">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Repair collected — Erin K.</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="12" hidden="1" outlineLevel="1">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Repair collected — Noah B.</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="13" hidden="1" outlineLevel="1">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Repair collected — Grace L.</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="14" hidden="1" outlineLevel="1">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Repair collected — Theo H.</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="15" hidden="1" outlineLevel="1">
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Repair collected — Maya P.</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="4" t="n">
+        <v>450</v>
+      </c>
+    </row>
     <row r="16" hidden="1" outlineLevel="1">
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Dana R.</t>
+          <t>Repair collected — Owen C.</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>120</v>
+        <v>360</v>
       </c>
     </row>
     <row r="17" hidden="1" outlineLevel="1">
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Marcus T.</t>
+          <t>Repair collected — Ava D.</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>150</v>
+        <v>270</v>
       </c>
     </row>
     <row r="18" hidden="1" outlineLevel="1">
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Priya S.</t>
+          <t>Repair collected — Leo F.</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>270</v>
+        <v>240</v>
       </c>
     </row>
     <row r="19" hidden="1" outlineLevel="1">
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Liam O.</t>
+          <t>Repair collected — Nina V.</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
@@ -708,364 +709,384 @@
     <row r="20" hidden="1" outlineLevel="1">
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Sofia M.</t>
+          <t>Repair collected — Caleb G.</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>150</v>
+        <v>240</v>
       </c>
     </row>
     <row r="21" hidden="1" outlineLevel="1">
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Jamal W.</t>
+          <t>Repair collected — Ruth A.</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>360</v>
+        <v>485</v>
       </c>
     </row>
     <row r="22" hidden="1" outlineLevel="1">
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Erin K.</t>
+          <t>Repair collected — Sam Q.</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>225</v>
+        <v>390</v>
       </c>
     </row>
     <row r="23" hidden="1" outlineLevel="1">
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Noah B.</t>
+          <t>Repair collected — Westville Bike Share</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>210</v>
+        <v>500</v>
       </c>
     </row>
     <row r="24" hidden="1" outlineLevel="1">
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Grace L.</t>
+          <t>Parts bought — June</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>240</v>
+        <v>-500</v>
       </c>
     </row>
     <row r="25" hidden="1" outlineLevel="1">
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Theo H.</t>
+          <t>Parts bought — July</t>
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>240</v>
+        <v>-400</v>
       </c>
     </row>
     <row r="26" hidden="1" outlineLevel="1">
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Maya P.</t>
+          <t>Parts bought — August</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>450</v>
+        <v>-300</v>
       </c>
     </row>
     <row r="27" hidden="1" outlineLevel="1">
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Owen C.</t>
+          <t>Rent paid — June</t>
         </is>
       </c>
       <c r="D27" s="4" t="n">
-        <v>360</v>
+        <v>-650</v>
       </c>
     </row>
     <row r="28" hidden="1" outlineLevel="1">
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Ava D.</t>
+          <t>Rent paid — July</t>
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>270</v>
+        <v>-650</v>
       </c>
     </row>
     <row r="29" hidden="1" outlineLevel="1">
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Leo F.</t>
+          <t>Rent paid — August</t>
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>240</v>
+        <v>-650</v>
       </c>
     </row>
     <row r="30" hidden="1" outlineLevel="1">
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Nina V.</t>
+          <t>New repair tool</t>
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>300</v>
+        <v>-400</v>
       </c>
     </row>
     <row r="31" hidden="1" outlineLevel="1">
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Caleb G.</t>
+          <t>Credit card paid off</t>
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>240</v>
+        <v>-2030</v>
       </c>
     </row>
     <row r="32" hidden="1" outlineLevel="1">
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Repair collected — Ruth A.</t>
+          <t>Money taken out for personal use</t>
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="33" hidden="1" outlineLevel="1">
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>Repair collected — Sam Q.</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="34" hidden="1" outlineLevel="1">
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Repair collected — Westville Bike Share</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="35" hidden="1" outlineLevel="1">
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>Parts bought — June</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="36" hidden="1" outlineLevel="1">
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>Parts bought — July</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>-400</v>
-      </c>
-    </row>
-    <row r="37" hidden="1" outlineLevel="1">
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>Parts bought — August</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>-300</v>
-      </c>
-    </row>
-    <row r="38" hidden="1" outlineLevel="1">
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>Rent paid — June</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>-650</v>
-      </c>
-    </row>
-    <row r="39" hidden="1" outlineLevel="1">
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>Rent paid — July</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>-650</v>
-      </c>
-    </row>
-    <row r="40" hidden="1" outlineLevel="1">
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>Rent paid — August</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="n">
-        <v>-650</v>
-      </c>
-    </row>
-    <row r="41" hidden="1" outlineLevel="1">
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>New repair tool</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>-400</v>
-      </c>
-    </row>
-    <row r="42" hidden="1" outlineLevel="1">
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>Credit card paid off</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>-2030</v>
-      </c>
-    </row>
-    <row r="43" hidden="1" outlineLevel="1">
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>Money taken out for personal use</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="n">
         <v>-600</v>
       </c>
     </row>
-    <row r="44" collapsed="1">
-      <c r="B44" s="16" t="inlineStr">
+    <row r="33" collapsed="1">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>Balance, August 31, 2026</t>
         </is>
       </c>
-      <c r="C44" s="17" t="n"/>
-      <c r="D44" s="13">
-        <f>SUBTOTAL(9,D3:D43)</f>
+      <c r="C33" s="17" t="n"/>
+      <c r="D33" s="13">
+        <f>D4+SUM(D5:D32)</f>
         <v>620</v>
         <v/>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="6" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="7" t="n"/>
+      <c r="D34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="7" t="n"/>
+      <c r="D35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>Right of Use</t>
         </is>
       </c>
+      <c r="C36" s="11" t="n"/>
+      <c r="D36" s="11" t="n"/>
+    </row>
+    <row r="37" hidden="1" outlineLevel="1">
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Company received at formation (June 1)</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="38" collapsed="1">
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>Balance, June 1, 2026</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="n"/>
+      <c r="D38" s="13">
+        <f>SUM(D37:D37)</f>
+        <v>650</v>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="16" t="inlineStr">
+        <is>
+          <t>Balance, August 31, 2026</t>
+        </is>
+      </c>
+      <c r="C39" s="17" t="n"/>
+      <c r="D39" s="13">
+        <f>D38</f>
+        <v>650</v>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="7" t="n"/>
+      <c r="D40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Parts</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="n"/>
+      <c r="D41" s="11" t="n"/>
+    </row>
+    <row r="42" hidden="1" outlineLevel="1">
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Company received at formation (June 1)</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="43" collapsed="1">
+      <c r="B43" s="16" t="inlineStr">
+        <is>
+          <t>Balance, June 1, 2026</t>
+        </is>
+      </c>
+      <c r="C43" s="17" t="n"/>
+      <c r="D43" s="13">
+        <f>SUM(D42:D42)</f>
+        <v>200</v>
+        <v/>
+      </c>
+    </row>
+    <row r="44" hidden="1" outlineLevel="1">
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Chains ×10 (June)</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="n"/>
+      <c r="D44" s="4" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="45" hidden="1" outlineLevel="1">
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>11-spd cassettes ×4 (June)</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="46" hidden="1" outlineLevel="1">
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Brake pad sets ×12 (June)</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="47" hidden="1" outlineLevel="1">
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Cables + housing (assorted) (June)</t>
+        </is>
+      </c>
       <c r="C47" s="11" t="n"/>
-      <c r="D47" s="11" t="n"/>
+      <c r="D47" s="4" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="48" hidden="1" outlineLevel="1">
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Last month's rent, paid in advance (on deposit)</t>
+          <t>Tubes ×10 (June)</t>
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="49" collapsed="1">
-      <c r="B49" s="16" t="inlineStr">
-        <is>
-          <t>Balance, June 1, 2026</t>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="49" hidden="1" outlineLevel="1">
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Chainrings + jockey wheels (July)</t>
         </is>
       </c>
       <c r="C49" s="17" t="n"/>
-      <c r="D49" s="13">
-        <f>D48</f>
-        <v>650</v>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="16" t="inlineStr">
-        <is>
-          <t>Balance, August 31, 2026</t>
+      <c r="D49" s="4" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="50" hidden="1" outlineLevel="1">
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Bottom brackets ×3 (July)</t>
         </is>
       </c>
       <c r="C50" s="17" t="n"/>
-      <c r="D50" s="13">
-        <f>D48</f>
-        <v>650</v>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>Parts</t>
+      <c r="D50" s="4" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="51" hidden="1" outlineLevel="1">
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Shift cables + housing (July)</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="52" hidden="1" outlineLevel="1">
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Tubeless sealant + valves (July)</t>
         </is>
       </c>
       <c r="C52" s="11" t="n"/>
-      <c r="D52" s="11" t="n"/>
+      <c r="D52" s="4" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="53" hidden="1" outlineLevel="1">
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Chains</t>
+          <t>Spokes + nipples (July)</t>
         </is>
       </c>
       <c r="D53" s="4" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="54" hidden="1" outlineLevel="1">
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Brake pads</t>
+          <t>Tires ×4 (August)</t>
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>40</v>
+        <v>130</v>
       </c>
     </row>
     <row r="55" hidden="1" outlineLevel="1">
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Derailleur cables</t>
+          <t>Brake pads (assorted) (August)</t>
         </is>
       </c>
       <c r="D55" s="4" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
     </row>
     <row r="56" hidden="1" outlineLevel="1">
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Cassettes</t>
+          <t>Cables + housing (August)</t>
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57" hidden="1" outlineLevel="1">
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Bottom brackets</t>
+          <t>Tubes ×8 (August)</t>
         </is>
       </c>
       <c r="D57" s="4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="58" hidden="1" outlineLevel="1">
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Spokes</t>
+          <t>Small parts (bolts, tape) (August)</t>
         </is>
       </c>
       <c r="D58" s="4" t="n">
@@ -1075,670 +1096,360 @@
     <row r="59" hidden="1" outlineLevel="1">
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Tubes</t>
+          <t>Parts used — Dana R.</t>
         </is>
       </c>
       <c r="D59" s="4" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="60" collapsed="1">
-      <c r="B60" s="16" t="inlineStr">
-        <is>
-          <t>Balance, June 1, 2026</t>
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="60" hidden="1" outlineLevel="1">
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Priya S.</t>
         </is>
       </c>
       <c r="C60" s="17" t="n"/>
-      <c r="D60" s="13">
-        <f>SUBTOTAL(9,D53:D59)</f>
+      <c r="D60" s="4" t="n">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="61" hidden="1" outlineLevel="1">
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Liam O.</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>-95</v>
+      </c>
+    </row>
+    <row r="62" hidden="1" outlineLevel="1">
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Jamal W.</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>-60</v>
+      </c>
+    </row>
+    <row r="63" hidden="1" outlineLevel="1">
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Erin K.</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="64" hidden="1" outlineLevel="1">
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Noah B.</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="n">
+        <v>-65</v>
+      </c>
+    </row>
+    <row r="65" hidden="1" outlineLevel="1">
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Grace L.</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>-35</v>
+      </c>
+    </row>
+    <row r="66" hidden="1" outlineLevel="1">
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Theo H.</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="67" hidden="1" outlineLevel="1">
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Maya P.</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>-125</v>
+      </c>
+    </row>
+    <row r="68" hidden="1" outlineLevel="1">
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Owen C.</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>-55</v>
+      </c>
+    </row>
+    <row r="69" hidden="1" outlineLevel="1">
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Ava D.</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>-45</v>
+      </c>
+    </row>
+    <row r="70" hidden="1" outlineLevel="1">
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Leo F.</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="71" hidden="1" outlineLevel="1">
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Nina V.</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="n">
+        <v>-80</v>
+      </c>
+    </row>
+    <row r="72" hidden="1" outlineLevel="1">
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Caleb G.</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="n">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="73" hidden="1" outlineLevel="1">
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Ruth A.</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="n">
+        <v>-129</v>
+      </c>
+    </row>
+    <row r="74" hidden="1" outlineLevel="1">
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Sam Q.</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>-70</v>
+      </c>
+    </row>
+    <row r="75" hidden="1" outlineLevel="1">
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Westville Bike Share</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>-105</v>
+      </c>
+    </row>
+    <row r="76" hidden="1" outlineLevel="1">
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — Ridgeline Trail Crew</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>-75</v>
+      </c>
+    </row>
+    <row r="77" hidden="1" outlineLevel="1">
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>Parts used — J. Smith</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>-36</v>
+      </c>
+    </row>
+    <row r="78" collapsed="1">
+      <c r="B78" s="16" t="inlineStr">
+        <is>
+          <t>Balance, August 31, 2026</t>
+        </is>
+      </c>
+      <c r="C78" s="17" t="n"/>
+      <c r="D78" s="13">
+        <f>D43+SUM(D44:D77)</f>
         <v>200</v>
         <v/>
       </c>
     </row>
-    <row r="61" hidden="1" outlineLevel="1">
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>Chains ×10 (June)</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="62" hidden="1" outlineLevel="1">
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>11-spd cassettes ×4 (June)</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="63" hidden="1" outlineLevel="1">
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>Brake pad sets ×12 (June)</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="64" hidden="1" outlineLevel="1">
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>Cables + housing (assorted) (June)</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="65" hidden="1" outlineLevel="1">
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>Tubes ×10 (June)</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="66" hidden="1" outlineLevel="1">
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>Chainrings + jockey wheels (July)</t>
-        </is>
-      </c>
-      <c r="D66" s="4" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="67" hidden="1" outlineLevel="1">
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>Bottom brackets ×3 (July)</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="n">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="68" hidden="1" outlineLevel="1">
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>Shift cables + housing (July)</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="69" hidden="1" outlineLevel="1">
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>Tubeless sealant + valves (July)</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="70" hidden="1" outlineLevel="1">
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>Spokes + nipples (July)</t>
-        </is>
-      </c>
-      <c r="D70" s="4" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="71" hidden="1" outlineLevel="1">
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>Tires ×4 (August)</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="n">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="72" hidden="1" outlineLevel="1">
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>Brake pads (assorted) (August)</t>
-        </is>
-      </c>
-      <c r="D72" s="4" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="73" hidden="1" outlineLevel="1">
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>Cables + housing (August)</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="74" hidden="1" outlineLevel="1">
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>Tubes ×8 (August)</t>
-        </is>
-      </c>
-      <c r="D74" s="4" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="75" hidden="1" outlineLevel="1">
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>Small parts (bolts, tape) (August)</t>
-        </is>
-      </c>
-      <c r="D75" s="4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="76" hidden="1" outlineLevel="1">
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Dana R.</t>
-        </is>
-      </c>
-      <c r="D76" s="4" t="n">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="77" hidden="1" outlineLevel="1">
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Priya S.</t>
-        </is>
-      </c>
-      <c r="D77" s="4" t="n">
-        <v>-25</v>
-      </c>
-    </row>
-    <row r="78" hidden="1" outlineLevel="1">
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Liam O.</t>
-        </is>
-      </c>
-      <c r="D78" s="4" t="n">
-        <v>-95</v>
-      </c>
-    </row>
-    <row r="79" hidden="1" outlineLevel="1">
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Jamal W.</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="n">
-        <v>-60</v>
-      </c>
-    </row>
-    <row r="80" hidden="1" outlineLevel="1">
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Erin K.</t>
-        </is>
-      </c>
-      <c r="D80" s="4" t="n">
-        <v>-40</v>
-      </c>
+    <row r="79">
+      <c r="B79" s="3" t="n"/>
+      <c r="D79" s="4" t="n"/>
+    </row>
+    <row r="80">
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>Tools &amp; Repair Equipment</t>
+        </is>
+      </c>
+      <c r="C80" s="11" t="n"/>
+      <c r="D80" s="11" t="n"/>
     </row>
     <row r="81" hidden="1" outlineLevel="1">
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Parts used — Noah B.</t>
+          <t>Company received at formation (June 1)</t>
         </is>
       </c>
       <c r="D81" s="4" t="n">
-        <v>-65</v>
-      </c>
-    </row>
-    <row r="82" hidden="1" outlineLevel="1">
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Grace L.</t>
-        </is>
-      </c>
-      <c r="D82" s="4" t="n">
-        <v>-35</v>
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="82" collapsed="1">
+      <c r="B82" s="16" t="inlineStr">
+        <is>
+          <t>Balance, June 1, 2026</t>
+        </is>
+      </c>
+      <c r="C82" s="17" t="n"/>
+      <c r="D82" s="13">
+        <f>SUM(D81:D81)</f>
+        <v>1200</v>
+        <v/>
       </c>
     </row>
     <row r="83" hidden="1" outlineLevel="1">
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Parts used — Theo H.</t>
+          <t>New repair tool bought this season</t>
         </is>
       </c>
       <c r="D83" s="4" t="n">
-        <v>-25</v>
-      </c>
-    </row>
-    <row r="84" hidden="1" outlineLevel="1">
-      <c r="B84" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Maya P.</t>
-        </is>
-      </c>
-      <c r="D84" s="4" t="n">
-        <v>-125</v>
-      </c>
-    </row>
-    <row r="85" hidden="1" outlineLevel="1">
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Owen C.</t>
-        </is>
-      </c>
-      <c r="D85" s="4" t="n">
-        <v>-55</v>
-      </c>
-    </row>
-    <row r="86" hidden="1" outlineLevel="1">
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Ava D.</t>
-        </is>
-      </c>
-      <c r="D86" s="4" t="n">
-        <v>-45</v>
-      </c>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="84" collapsed="1">
+      <c r="B84" s="16" t="inlineStr">
+        <is>
+          <t>Balance, August 31, 2026</t>
+        </is>
+      </c>
+      <c r="C84" s="17" t="n"/>
+      <c r="D84" s="13">
+        <f>D82+SUM(D83:D83)</f>
+        <v>1600</v>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="3" t="n"/>
+      <c r="D85" s="4" t="n"/>
+    </row>
+    <row r="86">
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>Fixtures</t>
+        </is>
+      </c>
+      <c r="C86" s="11" t="n"/>
+      <c r="D86" s="11" t="n"/>
     </row>
     <row r="87" hidden="1" outlineLevel="1">
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Parts used — Leo F.</t>
+          <t>Company received at formation (June 1)</t>
         </is>
       </c>
       <c r="D87" s="4" t="n">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="88" hidden="1" outlineLevel="1">
-      <c r="B88" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Nina V.</t>
-        </is>
-      </c>
-      <c r="D88" s="4" t="n">
-        <v>-80</v>
-      </c>
-    </row>
-    <row r="89" hidden="1" outlineLevel="1">
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Caleb G.</t>
-        </is>
-      </c>
-      <c r="D89" s="4" t="n">
-        <v>-25</v>
-      </c>
-    </row>
-    <row r="90" hidden="1" outlineLevel="1">
-      <c r="B90" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Ruth A.</t>
-        </is>
-      </c>
-      <c r="D90" s="4" t="n">
-        <v>-129</v>
-      </c>
-    </row>
-    <row r="91" hidden="1" outlineLevel="1">
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Sam Q.</t>
-        </is>
-      </c>
-      <c r="D91" s="4" t="n">
-        <v>-70</v>
-      </c>
+        <v>750</v>
+      </c>
+    </row>
+    <row r="88" collapsed="1">
+      <c r="B88" s="16" t="inlineStr">
+        <is>
+          <t>Balance, June 1, 2026</t>
+        </is>
+      </c>
+      <c r="C88" s="17" t="n"/>
+      <c r="D88" s="13">
+        <f>SUM(D87:D87)</f>
+        <v>750</v>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="16" t="inlineStr">
+        <is>
+          <t>Balance, August 31, 2026</t>
+        </is>
+      </c>
+      <c r="C89" s="17" t="n"/>
+      <c r="D89" s="13">
+        <f>D88</f>
+        <v>750</v>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="3" t="n"/>
+      <c r="D90" s="4" t="n"/>
+    </row>
+    <row r="91">
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="C91" s="11" t="n"/>
+      <c r="D91" s="11" t="n"/>
     </row>
     <row r="92" hidden="1" outlineLevel="1">
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Parts used — Westville Bike Share</t>
+          <t>Company received at formation (June 1)</t>
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>-105</v>
-      </c>
-    </row>
-    <row r="93" hidden="1" outlineLevel="1">
-      <c r="B93" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — Ridgeline Trail Crew</t>
-        </is>
-      </c>
-      <c r="D93" s="4" t="n">
-        <v>-75</v>
-      </c>
-    </row>
-    <row r="94" hidden="1" outlineLevel="1">
-      <c r="B94" s="3" t="inlineStr">
-        <is>
-          <t>Parts used — J. Smith</t>
-        </is>
-      </c>
-      <c r="D94" s="4" t="n">
-        <v>-36</v>
-      </c>
-    </row>
-    <row r="95" collapsed="1">
-      <c r="B95" s="16" t="inlineStr">
-        <is>
-          <t>Balance, August 31, 2026</t>
-        </is>
-      </c>
-      <c r="C95" s="17" t="n"/>
-      <c r="D95" s="13">
-        <f>SUBTOTAL(9,D53:D94)</f>
-        <v>200</v>
-        <v/>
-      </c>
-    </row>
-    <row r="97">
-      <c r="B97" s="6" t="inlineStr">
-        <is>
-          <t>Tools &amp; Repair Equipment</t>
-        </is>
-      </c>
-      <c r="C97" s="11" t="n"/>
-      <c r="D97" s="11" t="n"/>
-    </row>
-    <row r="98" hidden="1" outlineLevel="1">
-      <c r="B98" s="3" t="inlineStr">
-        <is>
-          <t>Repair stand</t>
-        </is>
-      </c>
-      <c r="D98" s="4" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="99" hidden="1" outlineLevel="1">
-      <c r="B99" s="3" t="inlineStr">
-        <is>
-          <t>Air compressor</t>
-        </is>
-      </c>
-      <c r="D99" s="4" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="100" hidden="1" outlineLevel="1">
-      <c r="B100" s="3" t="inlineStr">
-        <is>
-          <t>Parts washer</t>
-        </is>
-      </c>
-      <c r="D100" s="4" t="n">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="101" hidden="1" outlineLevel="1">
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t>Wheel-truing stand</t>
-        </is>
-      </c>
-      <c r="D101" s="4" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="102" hidden="1" outlineLevel="1">
-      <c r="B102" s="3" t="inlineStr">
-        <is>
-          <t>Cone wrench set</t>
-        </is>
-      </c>
-      <c r="D102" s="4" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="103" hidden="1" outlineLevel="1">
-      <c r="B103" s="3" t="inlineStr">
-        <is>
-          <t>Torque wrench</t>
-        </is>
-      </c>
-      <c r="D103" s="4" t="n">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="104" hidden="1" outlineLevel="1">
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>Hex/Allen set</t>
-        </is>
-      </c>
-      <c r="D104" s="4" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="105" hidden="1" outlineLevel="1">
-      <c r="B105" s="3" t="inlineStr">
-        <is>
-          <t>Cable cutters</t>
-        </is>
-      </c>
-      <c r="D105" s="4" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="106" hidden="1" outlineLevel="1">
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>Chain breaker</t>
-        </is>
-      </c>
-      <c r="D106" s="4" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="107" hidden="1" outlineLevel="1">
-      <c r="B107" s="3" t="inlineStr">
-        <is>
-          <t>Tire levers</t>
-        </is>
-      </c>
-      <c r="D107" s="4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="108" hidden="1" outlineLevel="1">
-      <c r="B108" s="3" t="inlineStr">
-        <is>
-          <t>Bench grinder</t>
-        </is>
-      </c>
-      <c r="D108" s="4" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="109" hidden="1" outlineLevel="1">
-      <c r="B109" s="3" t="inlineStr">
-        <is>
-          <t>Headset press</t>
-        </is>
-      </c>
-      <c r="D109" s="4" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="110" hidden="1" outlineLevel="1">
-      <c r="B110" s="3" t="inlineStr">
-        <is>
-          <t>Shop vacuum</t>
-        </is>
-      </c>
-      <c r="D110" s="4" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="111" collapsed="1">
-      <c r="B111" s="16" t="inlineStr">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="93" collapsed="1">
+      <c r="B93" s="16" t="inlineStr">
         <is>
           <t>Balance, June 1, 2026</t>
         </is>
       </c>
-      <c r="C111" s="17" t="n"/>
-      <c r="D111" s="13">
-        <f>SUBTOTAL(9,D98:D110)</f>
-        <v>1200</v>
-        <v/>
-      </c>
-    </row>
-    <row r="112" hidden="1" outlineLevel="1">
-      <c r="B112" s="3" t="inlineStr">
-        <is>
-          <t>New repair tool bought this season</t>
-        </is>
-      </c>
-      <c r="D112" s="4" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="113" collapsed="1">
-      <c r="B113" s="16" t="inlineStr">
-        <is>
-          <t>Balance, August 31, 2026</t>
-        </is>
-      </c>
-      <c r="C113" s="17" t="n"/>
-      <c r="D113" s="13">
-        <f>SUBTOTAL(9,D98:D112)</f>
-        <v>1600</v>
-        <v/>
-      </c>
-    </row>
-    <row r="115">
-      <c r="B115" s="6" t="inlineStr">
-        <is>
-          <t>Fixtures</t>
-        </is>
-      </c>
-      <c r="C115" s="11" t="n"/>
-      <c r="D115" s="11" t="n"/>
-    </row>
-    <row r="116" outlineLevel="1">
-      <c r="B116" s="3" t="inlineStr">
-        <is>
-          <t>Desk</t>
-        </is>
-      </c>
-      <c r="D116" s="4" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="117" outlineLevel="1">
-      <c r="B117" s="3" t="inlineStr">
-        <is>
-          <t>Shelving units</t>
-        </is>
-      </c>
-      <c r="D117" s="4" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="118" outlineLevel="1">
-      <c r="B118" s="3" t="inlineStr">
-        <is>
-          <t>Display rack</t>
-        </is>
-      </c>
-      <c r="D118" s="4" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="119" outlineLevel="1">
-      <c r="B119" s="3" t="inlineStr">
-        <is>
-          <t>Pegboard + hooks</t>
-        </is>
-      </c>
-      <c r="D119" s="4" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="B120" s="16" t="inlineStr">
-        <is>
-          <t>Balance, June 1, 2026</t>
-        </is>
-      </c>
-      <c r="C120" s="17" t="n"/>
-      <c r="D120" s="13">
-        <f>SUM(D116:D119)</f>
-        <v>750</v>
-        <v/>
-      </c>
-    </row>
-    <row r="121">
-      <c r="B121" s="16" t="inlineStr">
-        <is>
-          <t>Balance, August 31, 2026</t>
-        </is>
-      </c>
-      <c r="C121" s="17" t="n"/>
-      <c r="D121" s="13">
-        <f>SUM(D116:D119)</f>
-        <v>750</v>
-        <v/>
-      </c>
-    </row>
-    <row r="123">
-      <c r="B123" s="6" t="inlineStr">
-        <is>
-          <t>Laptop</t>
-        </is>
-      </c>
-      <c r="C123" s="11" t="n"/>
-      <c r="D123" s="11" t="n"/>
-    </row>
-    <row r="124" hidden="1" outlineLevel="1">
-      <c r="B124" s="3" t="inlineStr">
-        <is>
-          <t>Laptop (from home)</t>
-        </is>
-      </c>
-      <c r="D124" s="4" t="n">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="125" collapsed="1">
-      <c r="B125" s="16" t="inlineStr">
-        <is>
-          <t>Balance, June 1, 2026</t>
-        </is>
-      </c>
-      <c r="C125" s="17" t="n"/>
-      <c r="D125" s="13">
-        <f>SUM(D124)</f>
+      <c r="C93" s="17" t="n"/>
+      <c r="D93" s="13">
+        <f>SUM(D92:D92)</f>
         <v>610</v>
         <v/>
       </c>
     </row>
-    <row r="126">
-      <c r="B126" s="16" t="inlineStr">
+    <row r="94">
+      <c r="B94" s="16" t="inlineStr">
         <is>
           <t>Balance, August 31, 2026</t>
         </is>
       </c>
-      <c r="C126" s="17" t="n"/>
-      <c r="D126" s="13">
-        <f>SUM(D125)</f>
+      <c r="C94" s="17" t="n"/>
+      <c r="D94" s="13">
+        <f>D93</f>
         <v>610</v>
         <v/>
       </c>
@@ -1755,7 +1466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D17"/>
+  <dimension ref="B1:D12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1783,154 +1494,115 @@
     <row r="3" hidden="1" outlineLevel="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Charged — hand tools</t>
+          <t>Company assumed the claim at formation (June 1)</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="4" hidden="1" outlineLevel="1">
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Charged — air compressor</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>180</v>
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="4" collapsed="1">
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Balance, June 1, 2026</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="13">
+        <f>SUM(D3:D3)</f>
+        <v>2030</v>
+        <v/>
       </c>
     </row>
     <row r="5" hidden="1" outlineLevel="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Charged — parts washer</t>
+          <t>Paid off in full this season</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="6" hidden="1" outlineLevel="1">
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Charged — wheel-truing stand</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="7" hidden="1" outlineLevel="1">
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Charged — fixtures</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="8" hidden="1" outlineLevel="1">
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Charged — parts (QBP order)</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="9" collapsed="1">
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>Balance, June 1, 2026</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="n"/>
-      <c r="D9" s="13">
-        <f>SUM(D3:D8)</f>
-        <v>2030</v>
-        <v/>
-      </c>
-    </row>
-    <row r="10" hidden="1" outlineLevel="1">
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Paid off in full this season</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n">
         <v>-2030</v>
       </c>
     </row>
-    <row r="11" collapsed="1">
-      <c r="B11" s="16" t="inlineStr">
+    <row r="6" collapsed="1">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>Balance, August 31, 2026</t>
         </is>
       </c>
-      <c r="C11" s="17" t="n"/>
-      <c r="D11" s="13">
-        <f>SUM(D9:D10)</f>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="13">
+        <f>D4+SUM(D5:D5)</f>
         <v>0</v>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="6" t="inlineStr">
+    <row r="7">
+      <c r="B7" s="3" t="n"/>
+      <c r="D7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Customer Deposit</t>
         </is>
       </c>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-    </row>
-    <row r="14" hidden="1" outlineLevel="1">
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Smith's advance for a custom frame</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="n">
+      <c r="C8" s="11" t="n"/>
+      <c r="D8" s="11" t="n"/>
+    </row>
+    <row r="9" hidden="1" outlineLevel="1">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Company assumed the claim at formation (June 1)</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="4" t="n">
         <v>220</v>
       </c>
     </row>
-    <row r="15" collapsed="1">
-      <c r="B15" s="16" t="inlineStr">
+    <row r="10" collapsed="1">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Balance, June 1, 2026</t>
         </is>
       </c>
-      <c r="C15" s="17" t="n"/>
-      <c r="D15" s="13">
-        <f>SUM(D14)</f>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="13">
+        <f>SUM(D9:D9)</f>
         <v>220</v>
         <v/>
       </c>
     </row>
-    <row r="16" hidden="1" outlineLevel="1">
-      <c r="B16" s="3" t="inlineStr">
+    <row r="11" hidden="1" outlineLevel="1">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Built and delivered Smith's frame — no longer owed</t>
         </is>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="4" t="n">
         <v>-220</v>
       </c>
     </row>
-    <row r="17" collapsed="1">
-      <c r="B17" s="16" t="inlineStr">
+    <row r="12" collapsed="1">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>Balance, August 31, 2026</t>
         </is>
       </c>
-      <c r="C17" s="17" t="n"/>
-      <c r="D17" s="13">
-        <f>SUM(D15:D16)</f>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="13">
+        <f>D10+SUM(D11:D11)</f>
         <v>0</v>
         <v/>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Bike-Repair-Source-Workbooks/Bike-Repair-Module-3-1.xlsx
+++ b/Bike-Repair-Source-Workbooks/Bike-Repair-Module-3-1.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D94"/>
+  <dimension ref="A1:D94"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,7 @@
     <row r="3" hidden="1" outlineLevel="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Company received at formation (June 1)</t>
+          <t>additional contribution (Section 10)</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
@@ -552,7 +552,6 @@
       <c r="D4" s="13">
         <f>SUM(D3:D3)</f>
         <v>1300</v>
-        <v/>
       </c>
     </row>
     <row r="5" hidden="1" outlineLevel="1">
@@ -809,7 +808,7 @@
     <row r="30" hidden="1" outlineLevel="1">
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>New repair tool</t>
+          <t>Wheel truing stand</t>
         </is>
       </c>
       <c r="D30" s="4" t="n">
@@ -846,7 +845,6 @@
       <c r="D33" s="13">
         <f>D4+SUM(D5:D32)</f>
         <v>620</v>
-        <v/>
       </c>
     </row>
     <row r="34">
@@ -886,7 +884,6 @@
       <c r="D38" s="13">
         <f>SUM(D37:D37)</f>
         <v>650</v>
-        <v/>
       </c>
     </row>
     <row r="39">
@@ -899,7 +896,6 @@
       <c r="D39" s="13">
         <f>D38</f>
         <v>650</v>
-        <v/>
       </c>
     </row>
     <row r="40">
@@ -935,7 +931,6 @@
       <c r="D43" s="13">
         <f>SUM(D42:D42)</f>
         <v>200</v>
-        <v/>
       </c>
     </row>
     <row r="44" hidden="1" outlineLevel="1">
@@ -1294,7 +1289,6 @@
       <c r="D78" s="13">
         <f>D43+SUM(D44:D77)</f>
         <v>200</v>
-        <v/>
       </c>
     </row>
     <row r="79">
@@ -1330,13 +1324,12 @@
       <c r="D82" s="13">
         <f>SUM(D81:D81)</f>
         <v>1200</v>
-        <v/>
       </c>
     </row>
     <row r="83" hidden="1" outlineLevel="1">
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>New repair tool bought this season</t>
+          <t>Wheel truing stand bought this season</t>
         </is>
       </c>
       <c r="D83" s="4" t="n">
@@ -1353,7 +1346,6 @@
       <c r="D84" s="13">
         <f>D82+SUM(D83:D83)</f>
         <v>1600</v>
-        <v/>
       </c>
     </row>
     <row r="85">
@@ -1389,7 +1381,6 @@
       <c r="D88" s="13">
         <f>SUM(D87:D87)</f>
         <v>750</v>
-        <v/>
       </c>
     </row>
     <row r="89">
@@ -1402,7 +1393,6 @@
       <c r="D89" s="13">
         <f>D88</f>
         <v>750</v>
-        <v/>
       </c>
     </row>
     <row r="90">
@@ -1438,7 +1428,6 @@
       <c r="D93" s="13">
         <f>SUM(D92:D92)</f>
         <v>610</v>
-        <v/>
       </c>
     </row>
     <row r="94">
@@ -1451,7 +1440,6 @@
       <c r="D94" s="13">
         <f>D93</f>
         <v>610</v>
-        <v/>
       </c>
     </row>
   </sheetData>
@@ -1466,7 +1454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D12"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1511,7 +1499,6 @@
       <c r="D4" s="13">
         <f>SUM(D3:D3)</f>
         <v>2030</v>
-        <v/>
       </c>
     </row>
     <row r="5" hidden="1" outlineLevel="1">
@@ -1534,7 +1521,6 @@
       <c r="D6" s="13">
         <f>D4+SUM(D5:D5)</f>
         <v>0</v>
-        <v/>
       </c>
     </row>
     <row r="7">
@@ -1571,7 +1557,6 @@
       <c r="D10" s="13">
         <f>SUM(D9:D9)</f>
         <v>220</v>
-        <v/>
       </c>
     </row>
     <row r="11" hidden="1" outlineLevel="1">
@@ -1595,14 +1580,8 @@
       <c r="D12" s="13">
         <f>D10+SUM(D11:D11)</f>
         <v>0</v>
-        <v/>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1615,7 +1594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D63"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1643,7 +1622,7 @@
     <row r="3" hidden="1" outlineLevel="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Cash — Company received at formation (June 1)</t>
+          <t>Cash — additional contribution (Section 10)</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
@@ -1733,7 +1712,6 @@
       <c r="D11" s="13">
         <f>SUM(D3:D10)</f>
         <v>2460</v>
-        <v/>
       </c>
     </row>
     <row r="12">
@@ -1746,7 +1724,6 @@
       <c r="D12" s="13">
         <f>D11</f>
         <v>2460</v>
-        <v/>
       </c>
     </row>
     <row r="13">
@@ -2204,7 +2181,6 @@
       <c r="D58" s="13">
         <f>SUBTOTAL(9,D16:D57)</f>
         <v>2570</v>
-        <v/>
       </c>
     </row>
     <row r="59">
@@ -2251,7 +2227,6 @@
       <c r="D63" s="13">
         <f>SUM(D61:D62)</f>
         <v>-600</v>
-        <v/>
       </c>
     </row>
     <row r="67" hidden="1" outlineLevel="1"/>
@@ -2268,7 +2243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:C19"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
